--- a/Status.xlsx
+++ b/Status.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\jaya sri\A_Project_related\Daily_Status_\Daily_Standup_Status2_\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\jaya sri\A_Project_related\Daily_Status_\Data_Engineering\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C205A46-0F3E-4BDF-A715-4D3198F0923C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{213C6586-25E1-42B8-A7BC-391437CA297B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="84">
   <si>
     <t>Date</t>
   </si>
@@ -259,6 +259,24 @@
   </si>
   <si>
     <t>refresh error in power bi documentation prepare</t>
+  </si>
+  <si>
+    <t>2.tableau (hierarchy, groups, sets, cluster)-</t>
+  </si>
+  <si>
+    <t>1.tableau  table creation with filter</t>
+  </si>
+  <si>
+    <t>2.tableau (bins, histograms, sets and filter basics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.tableau kt to Fathima </t>
+  </si>
+  <si>
+    <t>1.tableau  filter  -- in progress</t>
+  </si>
+  <si>
+    <t>2.sql (table creation, insert into , where, update, not, in, alter table, alter column name)explanation to Santhosh -- completed</t>
   </si>
 </sst>
 </file>
@@ -598,7 +616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.6640625" style="1" customWidth="1"/>
@@ -1361,6 +1379,63 @@
         <v>77</v>
       </c>
       <c r="E74" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A75" s="3">
+        <v>45681</v>
+      </c>
+      <c r="B75" t="s">
+        <v>79</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B76" t="s">
+        <v>78</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A77" s="3">
+        <v>45684</v>
+      </c>
+      <c r="B77" t="s">
+        <v>81</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B78" t="s">
+        <v>80</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A79" s="3">
+        <v>45685</v>
+      </c>
+      <c r="B79" t="s">
+        <v>82</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B80" t="s">
+        <v>83</v>
+      </c>
+      <c r="E80" s="1" t="s">
         <v>33</v>
       </c>
     </row>

--- a/Status.xlsx
+++ b/Status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\jaya sri\A_Project_related\Daily_Status_\Data_Engineering\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{213C6586-25E1-42B8-A7BC-391437CA297B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFF34A76-7A2D-4522-B1CE-93B2B0B11CB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="87">
   <si>
     <t>Date</t>
   </si>
@@ -277,6 +277,15 @@
   </si>
   <si>
     <t>2.sql (table creation, insert into , where, update, not, in, alter table, alter column name)explanation to Santhosh -- completed</t>
+  </si>
+  <si>
+    <t>generating all types of graphes</t>
+  </si>
+  <si>
+    <t>sql class</t>
+  </si>
+  <si>
+    <t>group discussion on deep seek</t>
   </si>
 </sst>
 </file>
@@ -616,7 +625,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F83"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.6640625" style="1" customWidth="1"/>
@@ -1436,6 +1445,33 @@
         <v>83</v>
       </c>
       <c r="E80" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A81" s="3">
+        <v>45686</v>
+      </c>
+      <c r="B81" t="s">
+        <v>84</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B82" t="s">
+        <v>85</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B83" t="s">
+        <v>86</v>
+      </c>
+      <c r="E83" s="1" t="s">
         <v>33</v>
       </c>
     </row>

--- a/Status.xlsx
+++ b/Status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\jaya sri\A_Project_related\Daily_Status_\Data_Engineering\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFF34A76-7A2D-4522-B1CE-93B2B0B11CB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2187621F-0F0E-44E7-AE62-D0D53598A726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="89">
   <si>
     <t>Date</t>
   </si>
@@ -286,6 +286,12 @@
   </si>
   <si>
     <t>group discussion on deep seek</t>
+  </si>
+  <si>
+    <t>project task on saperating day, month, year in python</t>
+  </si>
+  <si>
+    <t>Tableau (filters, sorting data, parameters)</t>
   </si>
 </sst>
 </file>
@@ -625,7 +631,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.6640625" style="1" customWidth="1"/>
@@ -1472,6 +1478,25 @@
         <v>86</v>
       </c>
       <c r="E83" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A84" s="3">
+        <v>45687</v>
+      </c>
+      <c r="B84" t="s">
+        <v>87</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B85" t="s">
+        <v>88</v>
+      </c>
+      <c r="E85" s="1" t="s">
         <v>33</v>
       </c>
     </row>

--- a/Status.xlsx
+++ b/Status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\jaya sri\A_Project_related\Daily_Status_\Data_Engineering\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2187621F-0F0E-44E7-AE62-D0D53598A726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE3F9F4D-238D-4D0B-A646-ED197C680C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="92">
   <si>
     <t>Date</t>
   </si>
@@ -292,6 +292,15 @@
   </si>
   <si>
     <t>Tableau (filters, sorting data, parameters)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tableau parameters </t>
+  </si>
+  <si>
+    <t>sql class on order by</t>
+  </si>
+  <si>
+    <t>group discussion on github</t>
   </si>
 </sst>
 </file>
@@ -631,7 +640,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F85"/>
+  <dimension ref="A1:F88"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.6640625" style="1" customWidth="1"/>
@@ -1497,6 +1506,33 @@
         <v>88</v>
       </c>
       <c r="E85" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A86" s="3">
+        <v>45688</v>
+      </c>
+      <c r="B86" t="s">
+        <v>89</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B87" t="s">
+        <v>90</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B88" t="s">
+        <v>91</v>
+      </c>
+      <c r="E88" s="1" t="s">
         <v>33</v>
       </c>
     </row>
